--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0001T0006Z000C1N18_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0001T0006Z000C1N18_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>35.42763969658625</v>
+        <v>5.756991450695266</v>
       </c>
       <c r="D2" t="n">
-        <v>35.15117696928173</v>
+        <v>5.712066257508281</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
